--- a/training_survey_templates/001_gym_staff_training_effectiveness_survey--training_survey_templates.xlsx
+++ b/training_survey_templates/001_gym_staff_training_effectiveness_survey--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_0</t>
+          <t>staff_training_overall_quality</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Staff Training</t>
+          <t>Overall Quality of Training</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,64 +543,64 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>training_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Staff Training Category</t>
+          <t>How often do you attend training sessions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_2</t>
+          <t>training_topics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What topics do you typically attend training on?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_3</t>
+          <t>training_relevance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Training Type</t>
+          <t>How would you rate the relevance of the training to your job?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_4</t>
+          <t>skill_application</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How often do you train on this topic?</t>
+          <t>How often do you apply the skills learned from training in your work?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_5</t>
+          <t>feedback_performance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How would you rate the effectiveness of the training provided?</t>
+          <t>What feedback do you receive on your performance after training?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_6</t>
+          <t>effectiveness_improvement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How would you rate the relevance of the content to your role?</t>
+          <t>How would you rate the effectiveness of the training in improving your job performance?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_7</t>
+          <t>practice_opportunity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How would you rate the relevance of the content to your work activities?</t>
+          <t>How often do you get to practice what you learned from training?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_8</t>
+          <t>value_aspect</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How often do you get to use the skills you've learned from training in your work?</t>
+          <t>What is the most valuable aspect of the training provided?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,363 +727,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_9</t>
+          <t>materials_use</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you get feedback on your performance from the training provided?</t>
+          <t>How often do you get to use the training materials after training?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_10</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What do you do when there are gaps in your knowledge or skills?</t>
+          <t>What would you recommend to improve the training?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_11</t>
+          <t>worth_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Do you think the training is worth your time?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What is your role?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What is your department/section?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,245 +827,245 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_1_choices</t>
+          <t>staff_training_overall_quality_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_1_choices</t>
+          <t>staff_training_overall_quality_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>staff_training_overall_quality_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_3_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>every_week</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Every week</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>every_month</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Every 2 weeks</t>
+          <t>Every month</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>training_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>every_4_weeks</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Every 4 weeks</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_4_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Operations</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_5_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_6_choices</t>
+          <t>training_topics_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_6_choices</t>
+          <t>training_relevance_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_7_choices</t>
+          <t>training_relevance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_7_choices</t>
+          <t>training_relevance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>skill_application_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1082,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>skill_application_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1099,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>skill_application_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1116,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_8_choices</t>
+          <t>skill_application_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,493 +1133,289 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>feedback_performance_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>every_week</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Every week</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>feedback_performance_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Every 2 weeks</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>feedback_performance_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>every_4_weeks</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Every 4 weeks</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_9_choices</t>
+          <t>feedback_performance_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>effectiveness_improvement_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_10_choices</t>
+          <t>effectiveness_improvement_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>effectiveness_improvement_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trainer</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>practice_opportunity_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>trainer</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Trainer</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>practice_opportunity_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>assessor</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Assessor</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>practice_opportunity_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>assessor</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Assessor</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>form_12_choices</t>
+          <t>practice_opportunity_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>materials_use_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>management</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Management</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>materials_use_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>front_office</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Front Office</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>materials_use_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>back_office</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Back office</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>form_13_choices</t>
+          <t>materials_use_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>form_18_choices</t>
+          <t>worth_time_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>form_18_choices</t>
+          <t>worth_time_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>form_19_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>form_19_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>form_20_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>form_21_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>form_22_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>form_23_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>form_24_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
